--- a/public/crawlability-blenderpay-september-2026.xlsx
+++ b/public/crawlability-blenderpay-september-2026.xlsx
@@ -9,8 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סיכום פעולות" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="robots, sitemap, אינדוקס" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="תת-דומיינים" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מקורות" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מקורות" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39,7 +38,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -53,12 +52,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D1ECF1"/>
+        <fgColor rgb="00E2E3E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,7 +68,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -83,9 +77,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -456,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -487,42 +478,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>בינונית</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>לתקן את שורת ה-Sitemap בקובץ robots.txt: היא מצביעה על https://loans.blender.co.il/sitemap.xml.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>בינונית</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>daily.blenderpay.com: עותק של blenderpay.com ללא הגנה. להגדיר X-Robots-Tag: noindex או להגן בסיסמה.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>לבדיקה</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>לאשר שהעמוד המוגדר noindex אכן אמור להישאר מחוץ לאינדקס.</t>
+          <t>להסיר את שורת ה-Sitemap בקובץ robots.txt (מצביעה על https://loans.blender.co.il/sitemap.xml, דומיין אחר).</t>
         </is>
       </c>
     </row>
@@ -597,7 +558,7 @@
           <t>שורת Sitemap</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>https://loans.blender.co.il/sitemap.xml</t>
         </is>
@@ -651,7 +612,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>https://loans.blender.co.il/sitemap.xml</t>
         </is>
@@ -673,7 +634,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>https://loans.blender.co.il/post-sitemap.xml</t>
         </is>
@@ -695,7 +656,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>https://loans.blender.co.il/page-sitemap.xml</t>
         </is>
@@ -717,7 +678,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>https://loans.blender.co.il/attachment-sitemap.xml</t>
         </is>
@@ -739,7 +700,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>https://loans.blender.co.il/helpie_faq-sitemap.xml</t>
         </is>
@@ -761,7 +722,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>https://loans.blender.co.il/managments-sitemap.xml</t>
         </is>
@@ -783,7 +744,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>https://loans.blender.co.il/partner-sitemap.xml</t>
         </is>
@@ -805,7 +766,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>https://loans.blender.co.il/medias-sitemap.xml</t>
         </is>
@@ -827,7 +788,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>https://loans.blender.co.il/category-sitemap.xml</t>
         </is>
@@ -849,7 +810,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>https://loans.blender.co.il/helpie_faq_category-sitemap.xml</t>
         </is>
@@ -871,7 +832,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>https://loans.blender.co.il/author-sitemap.xml</t>
         </is>
@@ -910,7 +871,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>https://blenderpay.com/</t>
         </is>
@@ -920,7 +881,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>https://blenderpay.com/ (0 הפניות)</t>
         </is>
@@ -932,7 +893,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>http://blenderpay.com/</t>
         </is>
@@ -942,7 +903,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>https://blenderpay.com:443/ (1 הפניות)</t>
         </is>
@@ -954,7 +915,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>https://www.blenderpay.com/</t>
         </is>
@@ -964,7 +925,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>https://blenderpay.com:443/ (1 הפניות)</t>
         </is>
@@ -976,7 +937,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>http://www.blenderpay.com/</t>
         </is>
@@ -986,7 +947,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>https://blenderpay.com:443/ (2 הפניות)</t>
         </is>
@@ -1039,7 +1000,7 @@
           <t>canonical</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>https://blenderpay.com</t>
         </is>
@@ -1057,7 +1018,7 @@
           <t>BLender - Partner login</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>https://blenderpay.com/partnerLogin</t>
         </is>
@@ -1074,113 +1035,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>תת-דומיין</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>קוד</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>כותרת</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>meta robots</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>canonical</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>כתובות באינדקס (site:)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>סיווג</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>פעולה</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>עדיפות</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>daily.blenderpay.com</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>BLender â Holistic Embedded Finance Platform</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>עותק של האתר ללא noindex וללא canonical</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>עותק של blenderpay.com ללא הגנה. להגדיר X-Robots-Tag: noindex או להגן בסיסמה.</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>בינונית</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
